--- a/artfynd/A 18810-2026 artfynd.xlsx
+++ b/artfynd/A 18810-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7002066</v>
+        <v>7002070</v>
       </c>
       <c r="B2" t="n">
-        <v>89317</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3242</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428032.089876463</v>
+        <v>428152</v>
       </c>
       <c r="R2" t="n">
-        <v>6969427.177200082</v>
+        <v>6969110</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2013-09-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-09-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7002064</v>
+        <v>7002071</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428140.791563388</v>
+        <v>428178</v>
       </c>
       <c r="R3" t="n">
-        <v>6969439.412520403</v>
+        <v>6969358</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2013-09-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-09-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7002070</v>
+        <v>7002064</v>
       </c>
       <c r="B4" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428151.866825598</v>
+        <v>428141</v>
       </c>
       <c r="R4" t="n">
-        <v>6969109.741538385</v>
+        <v>6969439</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2013-09-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-09-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7002067</v>
+        <v>7002065</v>
       </c>
       <c r="B5" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428032.089876463</v>
+        <v>428141</v>
       </c>
       <c r="R5" t="n">
-        <v>6969427.177200082</v>
+        <v>6969439</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1046,9 @@
           <t>2013-09-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-09-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7002065</v>
+        <v>7002068</v>
       </c>
       <c r="B6" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428140.791563388</v>
+        <v>428003</v>
       </c>
       <c r="R6" t="n">
-        <v>6969439.412520403</v>
+        <v>6969421</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,19 +1147,9 @@
           <t>2013-09-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2013-09-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7002068</v>
+        <v>7002066</v>
       </c>
       <c r="B7" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428003.1392320158</v>
+        <v>428032</v>
       </c>
       <c r="R7" t="n">
-        <v>6969421.416602432</v>
+        <v>6969427</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,19 +1248,9 @@
           <t>2013-09-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2013-09-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7002069</v>
+        <v>7002067</v>
       </c>
       <c r="B8" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427983.2084165887</v>
+        <v>428032</v>
       </c>
       <c r="R8" t="n">
-        <v>6969430.535261814</v>
+        <v>6969427</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,19 +1349,9 @@
           <t>2013-09-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2013-09-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,6 +1375,107 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7002069</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lövberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>427983</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6969431</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2013-09-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2013-09-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 18810-2026 artfynd.xlsx
+++ b/artfynd/A 18810-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7002064</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7002065</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7002070</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7002071</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7002068</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7002066</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7002067</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,8 +1520,23 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7002069</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>